--- a/LuBan/Design/Datas/技能/GameEffect.xlsx
+++ b/LuBan/Design/Datas/技能/GameEffect.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -43,7 +43,10 @@
     <t>tags</t>
   </si>
   <si>
-    <t>test1</t>
+    <t>stack</t>
+  </si>
+  <si>
+    <t>magnitude</t>
   </si>
   <si>
     <t>##type</t>
@@ -58,6 +61,9 @@
     <t>GameEffectTags</t>
   </si>
   <si>
+    <t>GameEffectStack</t>
+  </si>
+  <si>
     <t>BaseMagnitude</t>
   </si>
   <si>
@@ -91,12 +97,30 @@
     <t>block_ge_with</t>
   </si>
   <si>
+    <t>stack_type</t>
+  </si>
+  <si>
+    <t>count_limit</t>
+  </si>
+  <si>
+    <t>refresh_duration_on_stack</t>
+  </si>
+  <si>
+    <t>refresh_period_on_stack</t>
+  </si>
+  <si>
+    <t>expire_type</t>
+  </si>
+  <si>
     <t>瞬间</t>
   </si>
   <si>
     <t>test1,test2</t>
   </si>
   <si>
+    <t>不堆叠</t>
+  </si>
+  <si>
     <t>AttrBasedMagnitude</t>
   </si>
   <si>
@@ -106,10 +130,22 @@
     <t>test3,test4</t>
   </si>
   <si>
+    <t>来源堆叠</t>
+  </si>
+  <si>
+    <t>删除单层</t>
+  </si>
+  <si>
     <t>SimpleFloatMagnitude</t>
   </si>
   <si>
     <t>时间</t>
+  </si>
+  <si>
+    <t>目标堆叠</t>
+  </si>
+  <si>
+    <t>删除全部</t>
   </si>
 </sst>
 </file>
@@ -122,7 +158,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +186,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -294,7 +337,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,6 +347,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,76 +727,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
@@ -750,10 +799,10 @@
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
@@ -762,10 +811,10 @@
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
@@ -774,10 +823,10 @@
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
@@ -786,10 +835,10 @@
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
@@ -798,11 +847,17 @@
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -815,16 +870,52 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1138,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="10.6666666666667" style="3" customWidth="1"/>
@@ -1146,20 +1237,29 @@
     <col min="3" max="3" width="30" style="3" customWidth="1"/>
     <col min="4" max="5" width="12.5555555555556" style="3" customWidth="1"/>
     <col min="6" max="6" width="20.4444444444444" style="3" customWidth="1"/>
-    <col min="7" max="14" width="23.2222222222222" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="7" max="13" width="23.2222222222222" style="3" customWidth="1"/>
+    <col min="14" max="14" width="12.2222222222222" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.1111111111111" style="3" customWidth="1"/>
+    <col min="16" max="16" width="30.1111111111111" style="3" customWidth="1"/>
+    <col min="17" max="17" width="27.7777777777778" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.5555555555556" style="3" customWidth="1"/>
+    <col min="19" max="19" width="23.2222222222222" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:17">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:22">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
       <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
@@ -1169,137 +1269,183 @@
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
       <c r="M1" s="7"/>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:17">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:22">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="4" t="s">
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="16.2" spans="1:17">
+    <row r="3" s="2" customFormat="1" ht="16.2" spans="1:22">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="F3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="G3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="H3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="I3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="J3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="K3" s="19" t="s">
         <v>19</v>
       </c>
+      <c r="L3" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:22">
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+        <v>27</v>
+      </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="3">
+        <v>1</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T4" s="3">
         <v>22</v>
       </c>
-      <c r="O4" s="3">
-        <v>22</v>
-      </c>
-      <c r="P4" s="3">
+      <c r="U4" s="3">
         <v>33</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="V4" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:22">
       <c r="B5" s="3">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D5" s="3">
         <v>10</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="3">
+        <v>33</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T5" s="3">
         <v>44</v>
       </c>
-      <c r="P5" s="3">
+      <c r="U5" s="3">
         <v>44</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="V5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:22">
       <c r="B6" s="3">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3">
         <v>20</v>
@@ -1311,26 +1457,37 @@
         <v>1</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="3">
+        <v>37</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="T6" s="3">
         <v>66</v>
       </c>
-      <c r="P6" s="3">
+      <c r="U6" s="3">
         <v>22</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="V6" s="3">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:M1"/>
-    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="S1:V1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:M2"/>
-    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="S2:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/LuBan/Design/Datas/技能/GameEffect.xlsx
+++ b/LuBan/Design/Datas/技能/GameEffect.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -46,7 +46,7 @@
     <t>stack</t>
   </si>
   <si>
-    <t>magnitude</t>
+    <t>*modifiers</t>
   </si>
   <si>
     <t>##type</t>
@@ -64,6 +64,33 @@
     <t>GameEffectStack</t>
   </si>
   <si>
+    <t>list,Modifiers</t>
+  </si>
+  <si>
+    <t>EGameEffectDurationType</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>(list#sep=,),string</t>
+  </si>
+  <si>
+    <t>EGameEffectStackType</t>
+  </si>
+  <si>
+    <t>EGameEffectStackExpireType</t>
+  </si>
+  <si>
+    <t>EAttributeId</t>
+  </si>
+  <si>
+    <t>EModifierOperation</t>
+  </si>
+  <si>
     <t>BaseMagnitude</t>
   </si>
   <si>
@@ -73,6 +100,9 @@
     <t>period</t>
   </si>
   <si>
+    <t>first_period_immediately</t>
+  </si>
+  <si>
     <t>period_ge</t>
   </si>
   <si>
@@ -112,6 +142,75 @@
     <t>expire_type</t>
   </si>
   <si>
+    <t>target_attr</t>
+  </si>
+  <si>
+    <t>operate</t>
+  </si>
+  <si>
+    <t>magenitude</t>
+  </si>
+  <si>
+    <t>$type</t>
+  </si>
+  <si>
+    <t>simple_float_k</t>
+  </si>
+  <si>
+    <t>simple_float_b</t>
+  </si>
+  <si>
+    <t>attr_based_attr</t>
+  </si>
+  <si>
+    <t>attr_based_k</t>
+  </si>
+  <si>
+    <t>attr_based_b</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>持续时间类型</t>
+  </si>
+  <si>
+    <t>持续时间</t>
+  </si>
+  <si>
+    <t>周期</t>
+  </si>
+  <si>
+    <t>第一周期立刻执行</t>
+  </si>
+  <si>
+    <t>周期效果</t>
+  </si>
+  <si>
+    <t>堆叠类型</t>
+  </si>
+  <si>
+    <t>总数限制</t>
+  </si>
+  <si>
+    <t>添加时刷新持续时间</t>
+  </si>
+  <si>
+    <t>添加时刷新周期时间</t>
+  </si>
+  <si>
+    <t>失效策略</t>
+  </si>
+  <si>
+    <t>目标属性</t>
+  </si>
+  <si>
+    <t>操作类型</t>
+  </si>
+  <si>
+    <t>计算器类型</t>
+  </si>
+  <si>
     <t>瞬间</t>
   </si>
   <si>
@@ -121,9 +220,18 @@
     <t>不堆叠</t>
   </si>
   <si>
+    <t>基础生命</t>
+  </si>
+  <si>
+    <t>Minus</t>
+  </si>
+  <si>
     <t>AttrBasedMagnitude</t>
   </si>
   <si>
+    <t>SimpleFloatMagnitude</t>
+  </si>
+  <si>
     <t>永久</t>
   </si>
   <si>
@@ -134,9 +242,6 @@
   </si>
   <si>
     <t>删除单层</t>
-  </si>
-  <si>
-    <t>SimpleFloatMagnitude</t>
   </si>
   <si>
     <t>时间</t>
@@ -337,7 +442,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,6 +457,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -359,6 +470,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,7 +856,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -757,16 +880,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="10">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
@@ -775,89 +898,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -867,13 +990,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -882,40 +1017,64 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1229,265 +1388,499 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="5"/>
+  <dimension ref="A1:AB10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="10.6666666666667" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="3" width="30" style="3" customWidth="1"/>
-    <col min="4" max="5" width="12.5555555555556" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.4444444444444" style="3" customWidth="1"/>
-    <col min="7" max="13" width="23.2222222222222" style="3" customWidth="1"/>
-    <col min="14" max="14" width="12.2222222222222" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.1111111111111" style="3" customWidth="1"/>
-    <col min="16" max="16" width="30.1111111111111" style="3" customWidth="1"/>
-    <col min="17" max="17" width="27.7777777777778" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.5555555555556" style="3" customWidth="1"/>
-    <col min="19" max="19" width="23.2222222222222" style="3" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="8.66666666666667" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4.33333333333333" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.88888888888889" style="4" customWidth="1"/>
+    <col min="4" max="4" width="30" style="4" customWidth="1"/>
+    <col min="5" max="5" width="10.4444444444444" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.22222222222222" style="4" customWidth="1"/>
+    <col min="7" max="7" width="28.2222222222222" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.7777777777778" style="4" customWidth="1"/>
+    <col min="9" max="11" width="20.6666666666667" style="4" customWidth="1"/>
+    <col min="12" max="12" width="21.8888888888889" style="4" customWidth="1"/>
+    <col min="13" max="15" width="20.6666666666667" style="4" customWidth="1"/>
+    <col min="16" max="16" width="26" style="4" customWidth="1"/>
+    <col min="17" max="17" width="13.1111111111111" style="4" customWidth="1"/>
+    <col min="18" max="18" width="30.1111111111111" style="4" customWidth="1"/>
+    <col min="19" max="19" width="27.7777777777778" style="4" customWidth="1"/>
+    <col min="20" max="20" width="33" style="4" customWidth="1"/>
+    <col min="21" max="21" width="14.4444444444444" style="4" customWidth="1"/>
+    <col min="22" max="22" width="23" style="4" customWidth="1"/>
+    <col min="23" max="23" width="25.4444444444444" style="4" customWidth="1"/>
+    <col min="24" max="24" width="16.5555555555556" style="4" customWidth="1"/>
+    <col min="25" max="25" width="16.6666666666667" style="4" customWidth="1"/>
+    <col min="26" max="26" width="17.2222222222222" style="4" customWidth="1"/>
+    <col min="27" max="27" width="14.6666666666667" style="4" customWidth="1"/>
+    <col min="28" max="28" width="14.7777777777778" style="4" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:22">
+    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="8" t="s">
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="10" t="s">
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="13"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:22">
+    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:28">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="15" t="s">
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="17" t="s">
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="21"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="16.2" spans="1:22">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="R3" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="S3" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="T3" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="W3" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="19" t="s">
+      <c r="F4" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="21"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z5" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA5" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB5" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="R6" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="S6" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="T6" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="R7" s="4">
+        <v>1</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>33</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="U8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8" s="4">
+        <v>33</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="4">
+        <v>10</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="4">
+        <v>1</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X9" s="4">
+        <v>44</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="B10" s="4">
+        <v>3</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="4">
         <v>20</v>
       </c>
-      <c r="M3" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="18" t="s">
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="S10" s="4">
+        <v>1</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X10" s="4">
+        <v>66</v>
+      </c>
+      <c r="Y10" s="4">
         <v>22</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" s="19"/>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="3">
-        <v>1</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T4" s="3">
-        <v>22</v>
-      </c>
-      <c r="U4" s="3">
-        <v>33</v>
-      </c>
-      <c r="V4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="B5" s="3">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="3">
-        <v>10</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>1</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T5" s="3">
-        <v>44</v>
-      </c>
-      <c r="U5" s="3">
-        <v>44</v>
-      </c>
-      <c r="V5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
-      <c r="B6" s="3">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="3">
-        <v>20</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T6" s="3">
-        <v>66</v>
-      </c>
-      <c r="U6" s="3">
-        <v>22</v>
-      </c>
-      <c r="V6" s="3">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="N1:R1"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:M2"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="S2:V2"/>
+  <mergeCells count="10">
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:AB2"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="W4:AB4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/LuBan/Design/Datas/技能/GameEffect.xlsx
+++ b/LuBan/Design/Datas/技能/GameEffect.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -263,7 +263,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,21 +272,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <color theme="8" tint="0.6"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -451,6 +457,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -463,12 +481,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -476,12 +488,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -850,231 +856,240 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1391,481 +1406,481 @@
   <dimension ref="A1:AB10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="4" customWidth="1"/>
-    <col min="2" max="2" width="4.33333333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="9.88888888888889" style="4" customWidth="1"/>
-    <col min="4" max="4" width="30" style="4" customWidth="1"/>
-    <col min="5" max="5" width="10.4444444444444" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.22222222222222" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.2222222222222" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.7777777777778" style="4" customWidth="1"/>
-    <col min="9" max="11" width="20.6666666666667" style="4" customWidth="1"/>
-    <col min="12" max="12" width="21.8888888888889" style="4" customWidth="1"/>
-    <col min="13" max="15" width="20.6666666666667" style="4" customWidth="1"/>
-    <col min="16" max="16" width="26" style="4" customWidth="1"/>
-    <col min="17" max="17" width="13.1111111111111" style="4" customWidth="1"/>
-    <col min="18" max="18" width="30.1111111111111" style="4" customWidth="1"/>
-    <col min="19" max="19" width="27.7777777777778" style="4" customWidth="1"/>
-    <col min="20" max="20" width="33" style="4" customWidth="1"/>
-    <col min="21" max="21" width="14.4444444444444" style="4" customWidth="1"/>
-    <col min="22" max="22" width="23" style="4" customWidth="1"/>
-    <col min="23" max="23" width="25.4444444444444" style="4" customWidth="1"/>
-    <col min="24" max="24" width="16.5555555555556" style="4" customWidth="1"/>
-    <col min="25" max="25" width="16.6666666666667" style="4" customWidth="1"/>
-    <col min="26" max="26" width="17.2222222222222" style="4" customWidth="1"/>
-    <col min="27" max="27" width="14.6666666666667" style="4" customWidth="1"/>
-    <col min="28" max="28" width="14.7777777777778" style="4" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="8.66666666666667" style="7" customWidth="1"/>
+    <col min="2" max="2" width="4.33333333333333" style="7" customWidth="1"/>
+    <col min="3" max="3" width="9.88888888888889" style="7" customWidth="1"/>
+    <col min="4" max="4" width="30" style="7" customWidth="1"/>
+    <col min="5" max="5" width="10.4444444444444" style="7" customWidth="1"/>
+    <col min="6" max="6" width="8.22222222222222" style="7" customWidth="1"/>
+    <col min="7" max="7" width="28.2222222222222" style="7" customWidth="1"/>
+    <col min="8" max="8" width="11.7777777777778" style="7" customWidth="1"/>
+    <col min="9" max="11" width="20.6666666666667" style="7" customWidth="1"/>
+    <col min="12" max="12" width="21.8888888888889" style="7" customWidth="1"/>
+    <col min="13" max="15" width="20.6666666666667" style="7" customWidth="1"/>
+    <col min="16" max="16" width="26" style="7" customWidth="1"/>
+    <col min="17" max="17" width="13.1111111111111" style="7" customWidth="1"/>
+    <col min="18" max="18" width="30.1111111111111" style="7" customWidth="1"/>
+    <col min="19" max="19" width="27.7777777777778" style="7" customWidth="1"/>
+    <col min="20" max="20" width="33" style="7" customWidth="1"/>
+    <col min="21" max="21" width="14.4444444444444" style="7" customWidth="1"/>
+    <col min="22" max="22" width="23" style="7" customWidth="1"/>
+    <col min="23" max="23" width="25.4444444444444" style="7" customWidth="1"/>
+    <col min="24" max="24" width="16.5555555555556" style="7" customWidth="1"/>
+    <col min="25" max="25" width="16.6666666666667" style="7" customWidth="1"/>
+    <col min="26" max="26" width="17.2222222222222" style="7" customWidth="1"/>
+    <col min="27" max="27" width="14.6666666666667" style="7" customWidth="1"/>
+    <col min="28" max="28" width="14.7777777777778" style="7" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.2" spans="1:28">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="4" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="7" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="10" t="s">
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="12" t="s">
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="13"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="16"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:28">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="4" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="14" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="15" t="s">
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="18" t="s">
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="19"/>
-      <c r="U2" s="20" t="s">
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="21"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="24"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.2" spans="1:28">
-      <c r="A3" s="1" t="s">
+    <row r="3" s="4" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="O3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="23" t="s">
+      <c r="P3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="Q3" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="R3" s="23" t="s">
+      <c r="R3" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="S3" s="23" t="s">
+      <c r="S3" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="T3" s="23" t="s">
+      <c r="T3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="24" t="s">
+      <c r="U3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="24" t="s">
+      <c r="V3" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="24" t="s">
+      <c r="W3" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="24"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.2" spans="1:28">
-      <c r="A4" s="2" t="s">
+    <row r="4" s="4" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="25" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="J4" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="L4" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="26" t="s">
+      <c r="M4" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="N4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="O4" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="P4" s="25" t="s">
+      <c r="P4" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" s="25" t="s">
+      <c r="Q4" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="R4" s="25" t="s">
+      <c r="R4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="25" t="s">
+      <c r="S4" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="T4" s="25" t="s">
+      <c r="T4" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="24" t="s">
+      <c r="U4" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="24" t="s">
+      <c r="V4" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="W4" s="27" t="s">
+      <c r="W4" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="21"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="23"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="24"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="16.2" spans="1:28">
-      <c r="A5" s="2" t="s">
+    <row r="5" s="5" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="29" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="X5" s="25" t="s">
+      <c r="X5" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="Y5" s="25" t="s">
+      <c r="Y5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="Z5" s="30" t="s">
+      <c r="Z5" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="AA5" s="30" t="s">
+      <c r="AA5" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="AB5" s="30" t="s">
+      <c r="AB5" s="33" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="16.2" spans="1:28">
-      <c r="A6" s="3" t="s">
+    <row r="6" s="6" customFormat="1" ht="16.2" spans="1:28">
+      <c r="A6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31" t="s">
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="Q6" s="31" t="s">
+      <c r="Q6" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="R6" s="31" t="s">
+      <c r="R6" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="S6" s="31" t="s">
+      <c r="S6" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="T6" s="31" t="s">
+      <c r="T6" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="U6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="V6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="W6" s="3" t="s">
+      <c r="W6" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:28">
-      <c r="B7" s="4">
+      <c r="B7" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="R7" s="4">
+      <c r="R7" s="7">
         <v>1</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="U7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="V7" s="4" t="s">
+      <c r="V7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="Z7" s="4" t="s">
+      <c r="Z7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="AA7" s="4">
+      <c r="AA7" s="7">
         <v>33</v>
       </c>
-      <c r="AB7" s="4">
+      <c r="AB7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:28">
-      <c r="U8" s="4" t="s">
+      <c r="U8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="V8" s="4" t="s">
+      <c r="V8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="X8" s="4">
+      <c r="X8" s="7">
         <v>33</v>
       </c>
-      <c r="Y8" s="4">
+      <c r="Y8" s="7">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:28">
-      <c r="B9" s="4">
+      <c r="B9" s="7">
         <v>2</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="7">
         <v>10</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="S9" s="4">
+      <c r="S9" s="7">
         <v>1</v>
       </c>
-      <c r="T9" s="4" t="s">
+      <c r="T9" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="U9" s="4" t="s">
+      <c r="U9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="V9" s="4" t="s">
+      <c r="V9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="W9" s="4" t="s">
+      <c r="W9" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="X9" s="4">
+      <c r="X9" s="7">
         <v>44</v>
       </c>
-      <c r="Y9" s="4">
+      <c r="Y9" s="7">
         <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:28">
-      <c r="B10" s="4">
+      <c r="B10" s="7">
         <v>3</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="7">
         <v>20</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="7">
         <v>1</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="7">
         <v>1</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="P10" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="S10" s="4">
+      <c r="S10" s="7">
         <v>1</v>
       </c>
-      <c r="T10" s="4" t="s">
+      <c r="T10" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="U10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="V10" s="4" t="s">
+      <c r="V10" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="W10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="X10" s="4">
+      <c r="X10" s="7">
         <v>66</v>
       </c>
-      <c r="Y10" s="4">
+      <c r="Y10" s="7">
         <v>22</v>
       </c>
     </row>
@@ -1882,6 +1897,11 @@
     <mergeCell ref="W3:AB3"/>
     <mergeCell ref="W4:AB4"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W7:W10">
+      <formula1>"AttrBasedMagnitude,SimpleFloatMagnitude"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1891,9 +1911,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/LuBan/Design/Datas/技能/GameEffect.xlsx
+++ b/LuBan/Design/Datas/技能/GameEffect.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -251,6 +251,18 @@
   </si>
   <si>
     <t>额外生命</t>
+  </si>
+  <si>
+    <t>最大法力</t>
+  </si>
+  <si>
+    <t>基础法力</t>
+  </si>
+  <si>
+    <t>法力加成</t>
+  </si>
+  <si>
+    <t>额外法力</t>
   </si>
   <si>
     <t>最大护盾</t>
@@ -1487,7 +1499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.66363636363636" style="7" customWidth="1"/>
@@ -1900,7 +1912,7 @@
         <v>68</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="V8" s="7" t="s">
         <v>70</v>
@@ -1909,13 +1921,13 @@
         <v>64</v>
       </c>
       <c r="Y8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="Z8" s="7" t="s">
+      <c r="AA8" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="AA8" s="7" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -1923,7 +1935,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>66</v>
@@ -1935,7 +1947,7 @@
         <v>68</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V9" s="7" t="s">
         <v>70</v>
@@ -1944,13 +1956,13 @@
         <v>64</v>
       </c>
       <c r="Y9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z9" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="Z9" s="7" t="s">
+      <c r="AA9" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="AA9" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -1958,7 +1970,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>66</v>
@@ -1970,7 +1982,7 @@
         <v>68</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V10" s="7" t="s">
         <v>70</v>
@@ -1979,13 +1991,13 @@
         <v>64</v>
       </c>
       <c r="Y10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z10" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="Z10" s="7" t="s">
+      <c r="AA10" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="AA10" s="7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -1993,7 +2005,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>66</v>
@@ -2005,7 +2017,7 @@
         <v>68</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V11" s="7" t="s">
         <v>70</v>
@@ -2014,13 +2026,13 @@
         <v>64</v>
       </c>
       <c r="Y11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z11" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="Z11" s="7" t="s">
+      <c r="AA11" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="AA11" s="7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -2028,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>66</v>
@@ -2040,7 +2052,7 @@
         <v>68</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="V12" s="7" t="s">
         <v>70</v>
@@ -2049,13 +2061,13 @@
         <v>64</v>
       </c>
       <c r="Y12" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z12" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="Z12" s="7" t="s">
+      <c r="AA12" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="AA12" s="7" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -2063,7 +2075,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>66</v>
@@ -2075,7 +2087,7 @@
         <v>68</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V13" s="7" t="s">
         <v>70</v>
@@ -2084,13 +2096,48 @@
         <v>64</v>
       </c>
       <c r="Y13" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z13" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="Z13" s="7" t="s">
+      <c r="AA13" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="AA13" s="7" t="s">
+    </row>
+    <row r="14" spans="1:27">
+      <c r="B14" s="7">
+        <v>8</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>103</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="V14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="W14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y14" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z14" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA14" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2124,12 +2171,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/LuBan/Design/Datas/技能/GameEffect.xlsx
+++ b/LuBan/Design/Datas/技能/GameEffect.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="111">
   <si>
     <t>##var</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>最大法力</t>
+  </si>
+  <si>
+    <t>MpMax</t>
   </si>
   <si>
     <t>基础法力</t>
@@ -1912,7 +1915,7 @@
         <v>68</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="V8" s="7" t="s">
         <v>70</v>
@@ -1921,13 +1924,13 @@
         <v>64</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AA8" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -1935,7 +1938,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>66</v>
@@ -1947,7 +1950,7 @@
         <v>68</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V9" s="7" t="s">
         <v>70</v>
@@ -1956,13 +1959,13 @@
         <v>64</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA9" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -1970,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>66</v>
@@ -1982,7 +1985,7 @@
         <v>68</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V10" s="7" t="s">
         <v>70</v>
@@ -1991,13 +1994,13 @@
         <v>64</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA10" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -2005,7 +2008,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>66</v>
@@ -2017,7 +2020,7 @@
         <v>68</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V11" s="7" t="s">
         <v>70</v>
@@ -2026,13 +2029,13 @@
         <v>64</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -2040,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>66</v>
@@ -2052,7 +2055,7 @@
         <v>68</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V12" s="7" t="s">
         <v>70</v>
@@ -2061,13 +2064,13 @@
         <v>64</v>
       </c>
       <c r="Y12" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA12" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -2075,7 +2078,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>66</v>
@@ -2087,7 +2090,7 @@
         <v>68</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="V13" s="7" t="s">
         <v>70</v>
@@ -2096,13 +2099,13 @@
         <v>64</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -2110,7 +2113,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>66</v>
@@ -2122,7 +2125,7 @@
         <v>68</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V14" s="7" t="s">
         <v>70</v>
@@ -2131,13 +2134,13 @@
         <v>64</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Z14" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AA14" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2171,12 +2174,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
